--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117613662</v>
+        <v>117613627</v>
       </c>
       <c r="B13" t="n">
-        <v>90782</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619585</v>
+        <v>619561</v>
       </c>
       <c r="R13" t="n">
-        <v>7215929</v>
+        <v>7215877</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117613592</v>
+        <v>117613662</v>
       </c>
       <c r="B14" t="n">
         <v>90782</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619538</v>
+        <v>619585</v>
       </c>
       <c r="R14" t="n">
-        <v>7215796</v>
+        <v>7215929</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117613627</v>
+        <v>117613592</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619561</v>
+        <v>619538</v>
       </c>
       <c r="R15" t="n">
-        <v>7215877</v>
+        <v>7215796</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117613752</v>
+        <v>117613679</v>
       </c>
       <c r="B16" t="n">
-        <v>103338</v>
+        <v>100070</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619576</v>
+        <v>619900</v>
       </c>
       <c r="R16" t="n">
-        <v>7215783</v>
+        <v>7215930</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117613718</v>
+        <v>117613745</v>
       </c>
       <c r="B17" t="n">
-        <v>104914</v>
+        <v>78480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619647</v>
+        <v>619575</v>
       </c>
       <c r="R17" t="n">
-        <v>7215800</v>
+        <v>7215781</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117613628</v>
+        <v>117613614</v>
       </c>
       <c r="B18" t="n">
-        <v>103338</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619547</v>
+        <v>619579</v>
       </c>
       <c r="R18" t="n">
-        <v>7215868</v>
+        <v>7215872</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117613679</v>
+        <v>117613752</v>
       </c>
       <c r="B19" t="n">
-        <v>100070</v>
+        <v>103338</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619900</v>
+        <v>619576</v>
       </c>
       <c r="R19" t="n">
-        <v>7215930</v>
+        <v>7215783</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117613745</v>
+        <v>117613718</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>104914</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619575</v>
+        <v>619647</v>
       </c>
       <c r="R20" t="n">
-        <v>7215781</v>
+        <v>7215800</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117613614</v>
+        <v>117613628</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>103338</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619579</v>
+        <v>619547</v>
       </c>
       <c r="R21" t="n">
-        <v>7215872</v>
+        <v>7215868</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -6966,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117613700</v>
+        <v>117613646</v>
       </c>
       <c r="B58" t="n">
-        <v>97836</v>
+        <v>79562</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,25 +6978,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619743</v>
+        <v>619566</v>
       </c>
       <c r="R58" t="n">
-        <v>7215916</v>
+        <v>7215964</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7078,10 +7078,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117613646</v>
+        <v>117613703</v>
       </c>
       <c r="B59" t="n">
-        <v>79562</v>
+        <v>97742</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7090,25 +7090,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619566</v>
+        <v>619686</v>
       </c>
       <c r="R59" t="n">
-        <v>7215964</v>
+        <v>7215905</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117613703</v>
+        <v>117613755</v>
       </c>
       <c r="B60" t="n">
-        <v>97742</v>
+        <v>57287</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,38 +7202,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619686</v>
+        <v>619586</v>
       </c>
       <c r="R60" t="n">
-        <v>7215905</v>
+        <v>7215778</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7265,7 +7270,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7275,7 +7280,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7302,10 +7307,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117613755</v>
+        <v>117613762</v>
       </c>
       <c r="B61" t="n">
-        <v>57287</v>
+        <v>100007</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7314,43 +7319,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>222771</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619586</v>
+        <v>619572</v>
       </c>
       <c r="R61" t="n">
-        <v>7215778</v>
+        <v>7215766</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7419,10 +7419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117613762</v>
+        <v>117613700</v>
       </c>
       <c r="B62" t="n">
-        <v>100007</v>
+        <v>97836</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619572</v>
+        <v>619743</v>
       </c>
       <c r="R62" t="n">
-        <v>7215766</v>
+        <v>7215916</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7531,10 +7531,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117613622</v>
+        <v>117613672</v>
       </c>
       <c r="B63" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7543,25 +7543,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619562</v>
+        <v>619640</v>
       </c>
       <c r="R63" t="n">
-        <v>7215860</v>
+        <v>7216000</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117613733</v>
+        <v>117613622</v>
       </c>
       <c r="B64" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7655,25 +7655,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619610</v>
+        <v>619562</v>
       </c>
       <c r="R64" t="n">
-        <v>7215807</v>
+        <v>7215860</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7755,7 +7755,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117613644</v>
+        <v>117613733</v>
       </c>
       <c r="B65" t="n">
         <v>79590</v>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619512</v>
+        <v>619610</v>
       </c>
       <c r="R65" t="n">
-        <v>7215959</v>
+        <v>7215807</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7979,10 +7979,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117613672</v>
+        <v>117613644</v>
       </c>
       <c r="B67" t="n">
-        <v>97836</v>
+        <v>79590</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7991,25 +7991,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619640</v>
+        <v>619512</v>
       </c>
       <c r="R67" t="n">
-        <v>7216000</v>
+        <v>7215959</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117613702</v>
+        <v>117613611</v>
       </c>
       <c r="B82" t="n">
-        <v>97742</v>
+        <v>79561</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9671,25 +9671,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619685</v>
+        <v>619568</v>
       </c>
       <c r="R82" t="n">
-        <v>7215904</v>
+        <v>7215856</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9771,10 +9771,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117613615</v>
+        <v>117613638</v>
       </c>
       <c r="B83" t="n">
-        <v>90464</v>
+        <v>79561</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9783,25 +9783,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619582</v>
+        <v>619503</v>
       </c>
       <c r="R83" t="n">
-        <v>7215879</v>
+        <v>7215952</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9883,10 +9883,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117613741</v>
+        <v>117613702</v>
       </c>
       <c r="B84" t="n">
-        <v>96791</v>
+        <v>97742</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9899,16 +9899,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>504</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619606</v>
+        <v>619685</v>
       </c>
       <c r="R84" t="n">
-        <v>7215798</v>
+        <v>7215904</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117613604</v>
+        <v>117613615</v>
       </c>
       <c r="B85" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10007,25 +10007,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619557</v>
+        <v>619582</v>
       </c>
       <c r="R85" t="n">
-        <v>7215839</v>
+        <v>7215879</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10107,10 +10107,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117613611</v>
+        <v>117613741</v>
       </c>
       <c r="B86" t="n">
-        <v>79561</v>
+        <v>96791</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10119,25 +10119,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619568</v>
+        <v>619606</v>
       </c>
       <c r="R86" t="n">
-        <v>7215856</v>
+        <v>7215798</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10219,10 +10219,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117613638</v>
+        <v>117613604</v>
       </c>
       <c r="B87" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619503</v>
+        <v>619557</v>
       </c>
       <c r="R87" t="n">
-        <v>7215952</v>
+        <v>7215839</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -13131,10 +13131,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117613635</v>
+        <v>117613610</v>
       </c>
       <c r="B113" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13147,21 +13147,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>619516</v>
+        <v>619566</v>
       </c>
       <c r="R113" t="n">
-        <v>7215928</v>
+        <v>7215850</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13243,10 +13243,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117613735</v>
+        <v>117613671</v>
       </c>
       <c r="B114" t="n">
-        <v>79561</v>
+        <v>100070</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13255,25 +13255,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13283,10 +13283,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>619601</v>
+        <v>619629</v>
       </c>
       <c r="R114" t="n">
-        <v>7215813</v>
+        <v>7215970</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13355,10 +13355,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117613729</v>
+        <v>117613599</v>
       </c>
       <c r="B115" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13367,25 +13367,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13395,10 +13395,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>619621</v>
+        <v>619602</v>
       </c>
       <c r="R115" t="n">
-        <v>7215805</v>
+        <v>7215855</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13467,10 +13467,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117613610</v>
+        <v>117613660</v>
       </c>
       <c r="B116" t="n">
-        <v>79562</v>
+        <v>97836</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13479,25 +13479,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>619566</v>
+        <v>619579</v>
       </c>
       <c r="R116" t="n">
-        <v>7215850</v>
+        <v>7215923</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117613671</v>
+        <v>117613635</v>
       </c>
       <c r="B117" t="n">
-        <v>100070</v>
+        <v>79561</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13591,25 +13591,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13619,10 +13619,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>619629</v>
+        <v>619516</v>
       </c>
       <c r="R117" t="n">
-        <v>7215970</v>
+        <v>7215928</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13691,10 +13691,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117613660</v>
+        <v>117613735</v>
       </c>
       <c r="B118" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13703,25 +13703,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13731,10 +13731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>619579</v>
+        <v>619601</v>
       </c>
       <c r="R118" t="n">
-        <v>7215923</v>
+        <v>7215813</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13803,10 +13803,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117613599</v>
+        <v>117613729</v>
       </c>
       <c r="B119" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13815,25 +13815,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13843,10 +13843,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>619602</v>
+        <v>619621</v>
       </c>
       <c r="R119" t="n">
-        <v>7215855</v>
+        <v>7215805</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14708,10 +14708,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117613589</v>
+        <v>117613732</v>
       </c>
       <c r="B127" t="n">
-        <v>90513</v>
+        <v>79597</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14720,25 +14720,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>619522</v>
+        <v>619610</v>
       </c>
       <c r="R127" t="n">
-        <v>7215799</v>
+        <v>7215808</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14820,10 +14820,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117613732</v>
+        <v>117613612</v>
       </c>
       <c r="B128" t="n">
-        <v>79597</v>
+        <v>79596</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14836,21 +14836,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14860,10 +14860,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>619610</v>
+        <v>619568</v>
       </c>
       <c r="R128" t="n">
-        <v>7215808</v>
+        <v>7215856</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14932,10 +14932,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117613612</v>
+        <v>117613642</v>
       </c>
       <c r="B129" t="n">
-        <v>79596</v>
+        <v>79561</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14944,25 +14944,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14972,10 +14972,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>619568</v>
+        <v>619510</v>
       </c>
       <c r="R129" t="n">
-        <v>7215856</v>
+        <v>7215959</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15007,7 +15007,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15044,10 +15044,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>117613642</v>
+        <v>117613645</v>
       </c>
       <c r="B130" t="n">
-        <v>79561</v>
+        <v>80437</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15060,21 +15060,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15084,10 +15084,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>619510</v>
+        <v>619553</v>
       </c>
       <c r="R130" t="n">
-        <v>7215959</v>
+        <v>7215972</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15156,10 +15156,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>117613645</v>
+        <v>117613589</v>
       </c>
       <c r="B131" t="n">
-        <v>80437</v>
+        <v>90513</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15172,21 +15172,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15196,10 +15196,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>619553</v>
+        <v>619522</v>
       </c>
       <c r="R131" t="n">
-        <v>7215972</v>
+        <v>7215799</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117613697</v>
+        <v>117613707</v>
       </c>
       <c r="B2" t="n">
-        <v>41207</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>215698</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsfältmätare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Xanthorhoe annotinata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619758</v>
+        <v>619690</v>
       </c>
       <c r="R2" t="n">
-        <v>7215908</v>
+        <v>7215909</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117613707</v>
+        <v>117613732</v>
       </c>
       <c r="B3" t="n">
-        <v>97755</v>
+        <v>79599</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619690</v>
+        <v>619610</v>
       </c>
       <c r="R3" t="n">
-        <v>7215909</v>
+        <v>7215808</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117613732</v>
+        <v>117613643</v>
       </c>
       <c r="B4" t="n">
         <v>79599</v>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619610</v>
+        <v>619510</v>
       </c>
       <c r="R4" t="n">
-        <v>7215808</v>
+        <v>7215959</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117613643</v>
+        <v>117613697</v>
       </c>
       <c r="B5" t="n">
-        <v>79599</v>
+        <v>41207</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>215698</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogsfältmätare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Xanthorhoe annotinata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Zetterstedt, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619510</v>
+        <v>619758</v>
       </c>
       <c r="R5" t="n">
-        <v>7215959</v>
+        <v>7215908</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117613635</v>
+        <v>117613690</v>
       </c>
       <c r="B6" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619516</v>
+        <v>619785</v>
       </c>
       <c r="R6" t="n">
-        <v>7215928</v>
+        <v>7215946</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117613649</v>
+        <v>117613598</v>
       </c>
       <c r="B7" t="n">
-        <v>79599</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619568</v>
+        <v>619605</v>
       </c>
       <c r="R7" t="n">
-        <v>7215965</v>
+        <v>7215860</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117613727</v>
+        <v>117613635</v>
       </c>
       <c r="B8" t="n">
-        <v>79564</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619625</v>
+        <v>619516</v>
       </c>
       <c r="R8" t="n">
-        <v>7215804</v>
+        <v>7215928</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117613745</v>
+        <v>117613649</v>
       </c>
       <c r="B9" t="n">
-        <v>78482</v>
+        <v>79599</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,25 +1480,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619575</v>
+        <v>619568</v>
       </c>
       <c r="R9" t="n">
-        <v>7215781</v>
+        <v>7215965</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117613640</v>
+        <v>117613727</v>
       </c>
       <c r="B10" t="n">
-        <v>79563</v>
+        <v>79564</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619508</v>
+        <v>619625</v>
       </c>
       <c r="R10" t="n">
-        <v>7215964</v>
+        <v>7215804</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117613655</v>
+        <v>117613745</v>
       </c>
       <c r="B11" t="n">
-        <v>90501</v>
+        <v>78482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619561</v>
+        <v>619575</v>
       </c>
       <c r="R11" t="n">
-        <v>7215911</v>
+        <v>7215781</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117613659</v>
+        <v>117613640</v>
       </c>
       <c r="B12" t="n">
-        <v>90501</v>
+        <v>79563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619577</v>
+        <v>619508</v>
       </c>
       <c r="R12" t="n">
-        <v>7215927</v>
+        <v>7215964</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117613608</v>
+        <v>117613655</v>
       </c>
       <c r="B13" t="n">
         <v>90501</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619551</v>
+        <v>619561</v>
       </c>
       <c r="R13" t="n">
-        <v>7215843</v>
+        <v>7215911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117613690</v>
+        <v>117613659</v>
       </c>
       <c r="B14" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619785</v>
+        <v>619577</v>
       </c>
       <c r="R14" t="n">
-        <v>7215946</v>
+        <v>7215927</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117613598</v>
+        <v>117613608</v>
       </c>
       <c r="B15" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619605</v>
+        <v>619551</v>
       </c>
       <c r="R15" t="n">
-        <v>7215860</v>
+        <v>7215843</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117613589</v>
+        <v>117613664</v>
       </c>
       <c r="B34" t="n">
-        <v>90515</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619522</v>
+        <v>619606</v>
       </c>
       <c r="R34" t="n">
-        <v>7215799</v>
+        <v>7215918</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117613677</v>
+        <v>117613629</v>
       </c>
       <c r="B35" t="n">
-        <v>100072</v>
+        <v>103340</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4400,21 +4400,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619887</v>
+        <v>619540</v>
       </c>
       <c r="R35" t="n">
-        <v>7215924</v>
+        <v>7215870</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4496,10 +4496,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117613671</v>
+        <v>117613589</v>
       </c>
       <c r="B36" t="n">
-        <v>100072</v>
+        <v>90515</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4508,25 +4508,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619629</v>
+        <v>619522</v>
       </c>
       <c r="R36" t="n">
-        <v>7215970</v>
+        <v>7215799</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117613664</v>
+        <v>117613677</v>
       </c>
       <c r="B37" t="n">
-        <v>97838</v>
+        <v>100072</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,25 +4620,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619606</v>
+        <v>619887</v>
       </c>
       <c r="R37" t="n">
-        <v>7215918</v>
+        <v>7215924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117613691</v>
+        <v>117613671</v>
       </c>
       <c r="B38" t="n">
-        <v>97859</v>
+        <v>100072</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>1365</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619783</v>
+        <v>619629</v>
       </c>
       <c r="R38" t="n">
-        <v>7215948</v>
+        <v>7215970</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5056,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117613629</v>
+        <v>117613691</v>
       </c>
       <c r="B41" t="n">
-        <v>103340</v>
+        <v>97859</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5072,21 +5072,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619540</v>
+        <v>619783</v>
       </c>
       <c r="R41" t="n">
-        <v>7215870</v>
+        <v>7215948</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16610,6 +16610,228 @@
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>120472131</v>
+      </c>
+      <c r="B144" t="n">
+        <v>100167</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Skirträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>619880</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7215932</v>
+      </c>
+      <c r="S144" t="n">
+        <v>61</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>AC-Sto-0200</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>120472538</v>
+      </c>
+      <c r="B145" t="n">
+        <v>97836</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>504</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Skirträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>619692</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7215904</v>
+      </c>
+      <c r="S145" t="n">
+        <v>22</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>AC-Sto-0204</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -16612,10 +16612,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120472131</v>
+        <v>120472538</v>
       </c>
       <c r="B144" t="n">
-        <v>100167</v>
+        <v>97836</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16628,21 +16628,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1365</v>
+        <v>504</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16652,13 +16652,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>619880</v>
+        <v>619692</v>
       </c>
       <c r="R144" t="n">
-        <v>7215932</v>
+        <v>7215904</v>
       </c>
       <c r="S144" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>AC-Sto-0200</t>
+          <t>AC-Sto-0204</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -16723,10 +16723,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120472538</v>
+        <v>120472131</v>
       </c>
       <c r="B145" t="n">
-        <v>97836</v>
+        <v>100167</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16739,21 +16739,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>504</v>
+        <v>1365</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>619692</v>
+        <v>619880</v>
       </c>
       <c r="R145" t="n">
-        <v>7215904</v>
+        <v>7215932</v>
       </c>
       <c r="S145" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>AC-Sto-0204</t>
+          <t>AC-Sto-0200</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -16612,10 +16612,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120472538</v>
+        <v>120472131</v>
       </c>
       <c r="B144" t="n">
-        <v>97836</v>
+        <v>100167</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16628,21 +16628,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>504</v>
+        <v>1365</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16652,13 +16652,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>619692</v>
+        <v>619880</v>
       </c>
       <c r="R144" t="n">
-        <v>7215904</v>
+        <v>7215932</v>
       </c>
       <c r="S144" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>AC-Sto-0204</t>
+          <t>AC-Sto-0200</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -16723,10 +16723,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120472131</v>
+        <v>120472538</v>
       </c>
       <c r="B145" t="n">
-        <v>100167</v>
+        <v>97836</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16739,21 +16739,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1365</v>
+        <v>504</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>619880</v>
+        <v>619692</v>
       </c>
       <c r="R145" t="n">
-        <v>7215932</v>
+        <v>7215904</v>
       </c>
       <c r="S145" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>AC-Sto-0200</t>
+          <t>AC-Sto-0204</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
